--- a/MR_UKBiobank/BinaryData/SA_Enrolment/gMR_dat.xlsx
+++ b/MR_UKBiobank/BinaryData/SA_Enrolment/gMR_dat.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="52">
   <si>
     <t>SNP</t>
   </si>
@@ -83,6 +83,12 @@
   </si>
   <si>
     <t>exposure</t>
+  </si>
+  <si>
+    <t>beta.exposure_corrected</t>
+  </si>
+  <si>
+    <t>se.exposure_corrected</t>
   </si>
   <si>
     <t>action</t>
@@ -291,28 +297,34 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
+      <c r="AA1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" t="s">
         <v>39</v>
       </c>
-      <c r="E2" t="s">
-        <v>37</v>
-      </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.063746</v>
+        <v>0.063746</v>
       </c>
       <c r="H2" t="n">
         <v>0.11320797341461863</v>
@@ -324,16 +336,16 @@
         <v>0.3861253893094979</v>
       </c>
       <c r="K2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="O2" t="n">
         <v>0.03974158279313367</v>
@@ -345,7 +357,7 @@
         <v>315944.0</v>
       </c>
       <c r="R2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -357,42 +369,48 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X2" t="n">
+        <v>0.063746</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.0113683673469388</v>
+      </c>
+      <c r="Z2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z2" t="e">
+      <c r="AA2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" t="s">
         <v>39</v>
       </c>
-      <c r="E3" t="s">
-        <v>37</v>
-      </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>0.039983</v>
+        <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
         <v>-0.06923308600316334</v>
@@ -404,16 +422,16 @@
         <v>0.2859114273415542</v>
       </c>
       <c r="K3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="O3" t="n">
         <v>0.03254520177317449</v>
@@ -425,7 +443,7 @@
         <v>315944.0</v>
       </c>
       <c r="R3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -437,42 +455,48 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="V3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X3" t="n">
+        <v>-0.042572</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.0144209183673469</v>
+      </c>
+      <c r="Z3" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z3" t="e">
+      <c r="AA3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" t="s">
         <v>40</v>
       </c>
-      <c r="E4" t="s">
-        <v>38</v>
-      </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H4" t="n">
         <v>0.15891464551332074</v>
@@ -484,16 +508,16 @@
         <v>0.41606265667333453</v>
       </c>
       <c r="K4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="O4" t="n">
         <v>0.045606863996996046</v>
@@ -505,7 +529,7 @@
         <v>315944.0</v>
       </c>
       <c r="R4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -517,42 +541,48 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X4" t="n">
+        <v>0.041722</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.00684234693877551</v>
+      </c>
+      <c r="Z4" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z4" t="e">
+      <c r="AA4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" t="s">
         <v>40</v>
       </c>
-      <c r="E5" t="s">
-        <v>38</v>
-      </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>0.066314</v>
+        <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
         <v>-0.10397134179674575</v>
@@ -564,16 +594,16 @@
         <v>0.07170574532195578</v>
       </c>
       <c r="K5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="O5" t="n">
         <v>0.04796820226881708</v>
@@ -585,7 +615,7 @@
         <v>315944.0</v>
       </c>
       <c r="R5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -597,42 +627,48 @@
         <v>0.0114775510204082</v>
       </c>
       <c r="V5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X5" t="n">
+        <v>-0.080535</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.0282632653061224</v>
+      </c>
+      <c r="Z5" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y5" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z5" t="e">
+      <c r="AA5" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" t="s">
         <v>40</v>
       </c>
-      <c r="E6" t="s">
-        <v>38</v>
-      </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>0.036955</v>
+        <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
         <v>-0.03545339169759979</v>
@@ -644,16 +680,16 @@
         <v>0.25553104347605904</v>
       </c>
       <c r="K6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="O6" t="n">
         <v>0.03233695930566997</v>
@@ -665,7 +701,7 @@
         <v>315944.0</v>
       </c>
       <c r="R6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -677,42 +713,48 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X6" t="n">
+        <v>-0.036955</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.00718163265306122</v>
+      </c>
+      <c r="Z6" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z6" t="e">
+      <c r="AA6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
         <v>39</v>
       </c>
-      <c r="E7" t="s">
-        <v>37</v>
-      </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>0.060792</v>
+        <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
         <v>-0.11333008059645083</v>
@@ -724,16 +766,16 @@
         <v>0.07857879877446636</v>
       </c>
       <c r="K7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="O7" t="n">
         <v>0.046260637728663574</v>
@@ -745,7 +787,7 @@
         <v>315944.0</v>
       </c>
       <c r="R7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -757,18 +799,24 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="V7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X7" t="n">
+        <v>-0.071191</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.0245357142857143</v>
+      </c>
+      <c r="Z7" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y7" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z7" t="e">
+      <c r="AA7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -859,28 +907,34 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
+      <c r="AA1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" t="s">
         <v>39</v>
       </c>
-      <c r="E2" t="s">
-        <v>37</v>
-      </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.063746</v>
+        <v>0.063746</v>
       </c>
       <c r="H2" t="n">
         <v>-0.00640896296765077</v>
@@ -892,16 +946,16 @@
         <v>0.38630181408322994</v>
       </c>
       <c r="K2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O2" t="n">
         <v>0.017743298151836128</v>
@@ -913,7 +967,7 @@
         <v>317626.0</v>
       </c>
       <c r="R2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -925,42 +979,48 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X2" t="n">
+        <v>0.063746</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.0113683673469388</v>
+      </c>
+      <c r="Z2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z2" t="e">
+      <c r="AA2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" t="s">
         <v>39</v>
       </c>
-      <c r="E3" t="s">
-        <v>37</v>
-      </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>0.039983</v>
+        <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
         <v>0.024098274429378872</v>
@@ -972,16 +1032,16 @@
         <v>0.28552133641452526</v>
       </c>
       <c r="K3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O3" t="n">
         <v>0.015073566416373536</v>
@@ -993,7 +1053,7 @@
         <v>317626.0</v>
       </c>
       <c r="R3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -1005,42 +1065,48 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="V3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X3" t="n">
+        <v>-0.042572</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.0144209183673469</v>
+      </c>
+      <c r="Z3" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z3" t="e">
+      <c r="AA3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" t="s">
         <v>40</v>
       </c>
-      <c r="E4" t="s">
-        <v>38</v>
-      </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H4" t="n">
         <v>-0.016300450396919127</v>
@@ -1052,16 +1118,16 @@
         <v>0.4161702757330949</v>
       </c>
       <c r="K4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O4" t="n">
         <v>0.01983774514641621</v>
@@ -1073,7 +1139,7 @@
         <v>317626.0</v>
       </c>
       <c r="R4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -1085,42 +1151,48 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X4" t="n">
+        <v>0.041722</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.00684234693877551</v>
+      </c>
+      <c r="Z4" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z4" t="e">
+      <c r="AA4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" t="s">
         <v>40</v>
       </c>
-      <c r="E5" t="s">
-        <v>38</v>
-      </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>0.066314</v>
+        <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
         <v>0.031915254592675156</v>
@@ -1132,16 +1204,16 @@
         <v>0.07146770100684453</v>
       </c>
       <c r="K5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O5" t="n">
         <v>0.021046780336491662</v>
@@ -1153,7 +1225,7 @@
         <v>317626.0</v>
       </c>
       <c r="R5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -1165,42 +1237,48 @@
         <v>0.0114775510204082</v>
       </c>
       <c r="V5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X5" t="n">
+        <v>-0.080535</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.0282632653061224</v>
+      </c>
+      <c r="Z5" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y5" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z5" t="e">
+      <c r="AA5" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" t="s">
         <v>40</v>
       </c>
-      <c r="E6" t="s">
-        <v>38</v>
-      </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>0.036955</v>
+        <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
         <v>0.023647811168193016</v>
@@ -1212,16 +1290,16 @@
         <v>0.25517432452003297</v>
       </c>
       <c r="K6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O6" t="n">
         <v>0.014901044887753442</v>
@@ -1233,7 +1311,7 @@
         <v>317626.0</v>
       </c>
       <c r="R6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -1245,42 +1323,48 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X6" t="n">
+        <v>-0.036955</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.00718163265306122</v>
+      </c>
+      <c r="Z6" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z6" t="e">
+      <c r="AA6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
         <v>39</v>
       </c>
-      <c r="E7" t="s">
-        <v>37</v>
-      </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>0.060792</v>
+        <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
         <v>0.024445683935007102</v>
@@ -1292,16 +1376,16 @@
         <v>0.07834528659492611</v>
       </c>
       <c r="K7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O7" t="n">
         <v>0.020318004866706867</v>
@@ -1313,7 +1397,7 @@
         <v>317626.0</v>
       </c>
       <c r="R7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -1325,18 +1409,24 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="V7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X7" t="n">
+        <v>-0.071191</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.0245357142857143</v>
+      </c>
+      <c r="Z7" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y7" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z7" t="e">
+      <c r="AA7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1427,28 +1517,34 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
+      <c r="AA1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" t="s">
         <v>39</v>
       </c>
-      <c r="E2" t="s">
-        <v>37</v>
-      </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.063746</v>
+        <v>0.063746</v>
       </c>
       <c r="H2" t="n">
         <v>-0.01101993481684144</v>
@@ -1460,16 +1556,16 @@
         <v>0.3862300865964806</v>
       </c>
       <c r="K2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O2" t="n">
         <v>0.02679158993325966</v>
@@ -1481,7 +1577,7 @@
         <v>316872.0</v>
       </c>
       <c r="R2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -1493,42 +1589,48 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X2" t="n">
+        <v>0.063746</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.0113683673469388</v>
+      </c>
+      <c r="Z2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z2" t="e">
+      <c r="AA2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" t="s">
         <v>39</v>
       </c>
-      <c r="E3" t="s">
-        <v>37</v>
-      </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>0.039983</v>
+        <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
         <v>0.021137580129547143</v>
@@ -1540,16 +1642,16 @@
         <v>0.2854528011310561</v>
       </c>
       <c r="K3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O3" t="n">
         <v>0.022792438480451423</v>
@@ -1561,7 +1663,7 @@
         <v>316872.0</v>
       </c>
       <c r="R3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -1573,42 +1675,48 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="V3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X3" t="n">
+        <v>-0.042572</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.0144209183673469</v>
+      </c>
+      <c r="Z3" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z3" t="e">
+      <c r="AA3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" t="s">
         <v>40</v>
       </c>
-      <c r="E4" t="s">
-        <v>38</v>
-      </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H4" t="n">
         <v>-0.025141604942097516</v>
@@ -1620,16 +1728,16 @@
         <v>0.41618224393445935</v>
       </c>
       <c r="K4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O4" t="n">
         <v>0.029897604744285104</v>
@@ -1641,7 +1749,7 @@
         <v>316872.0</v>
       </c>
       <c r="R4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -1653,42 +1761,48 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X4" t="n">
+        <v>0.041722</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.00684234693877551</v>
+      </c>
+      <c r="Z4" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z4" t="e">
+      <c r="AA4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" t="s">
         <v>40</v>
       </c>
-      <c r="E5" t="s">
-        <v>38</v>
-      </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>0.066314</v>
+        <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
         <v>0.023390982754306833</v>
@@ -1700,16 +1814,16 @@
         <v>0.07156044080890707</v>
       </c>
       <c r="K5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O5" t="n">
         <v>0.03188592316010013</v>
@@ -1721,7 +1835,7 @@
         <v>316872.0</v>
       </c>
       <c r="R5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -1733,42 +1847,48 @@
         <v>0.0114775510204082</v>
       </c>
       <c r="V5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X5" t="n">
+        <v>-0.080535</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.0282632653061224</v>
+      </c>
+      <c r="Z5" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y5" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z5" t="e">
+      <c r="AA5" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" t="s">
         <v>40</v>
       </c>
-      <c r="E6" t="s">
-        <v>38</v>
-      </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>0.036955</v>
+        <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
         <v>0.007619934041396579</v>
@@ -1780,16 +1900,16 @@
         <v>0.25519768234492163</v>
       </c>
       <c r="K6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O6" t="n">
         <v>0.022530111984744857</v>
@@ -1801,7 +1921,7 @@
         <v>316872.0</v>
       </c>
       <c r="R6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -1813,42 +1933,48 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X6" t="n">
+        <v>-0.036955</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.00718163265306122</v>
+      </c>
+      <c r="Z6" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z6" t="e">
+      <c r="AA6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
         <v>39</v>
       </c>
-      <c r="E7" t="s">
-        <v>37</v>
-      </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>0.060792</v>
+        <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
         <v>0.02604819288088866</v>
@@ -1860,16 +1986,16 @@
         <v>0.07841336564922113</v>
       </c>
       <c r="K7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O7" t="n">
         <v>0.03069748009021115</v>
@@ -1881,7 +2007,7 @@
         <v>316872.0</v>
       </c>
       <c r="R7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -1893,18 +2019,24 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="V7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X7" t="n">
+        <v>-0.071191</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.0245357142857143</v>
+      </c>
+      <c r="Z7" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y7" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z7" t="e">
+      <c r="AA7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1995,28 +2127,34 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
+      <c r="AA1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" t="s">
         <v>39</v>
       </c>
-      <c r="E2" t="s">
-        <v>37</v>
-      </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.063746</v>
+        <v>0.063746</v>
       </c>
       <c r="H2" t="n">
         <v>0.014914633384528763</v>
@@ -2028,16 +2166,16 @@
         <v>0.38618630916458313</v>
       </c>
       <c r="K2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O2" t="n">
         <v>0.03126456969611048</v>
@@ -2049,7 +2187,7 @@
         <v>324772.0</v>
       </c>
       <c r="R2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -2061,42 +2199,48 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X2" t="n">
+        <v>0.063746</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.0113683673469388</v>
+      </c>
+      <c r="Z2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z2" t="e">
+      <c r="AA2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" t="s">
         <v>39</v>
       </c>
-      <c r="E3" t="s">
-        <v>37</v>
-      </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>0.039983</v>
+        <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
         <v>-0.0244839522940332</v>
@@ -2108,16 +2252,16 @@
         <v>0.2855695688051926</v>
       </c>
       <c r="K3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O3" t="n">
         <v>0.02632983385451268</v>
@@ -2129,7 +2273,7 @@
         <v>324772.0</v>
       </c>
       <c r="R3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -2141,42 +2285,48 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="V3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X3" t="n">
+        <v>-0.042572</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.0144209183673469</v>
+      </c>
+      <c r="Z3" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z3" t="e">
+      <c r="AA3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" t="s">
         <v>40</v>
       </c>
-      <c r="E4" t="s">
-        <v>38</v>
-      </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H4" t="n">
         <v>0.00197716985396096</v>
@@ -2188,16 +2338,16 @@
         <v>0.4161303930141761</v>
       </c>
       <c r="K4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O4" t="n">
         <v>0.034957411930060966</v>
@@ -2209,7 +2359,7 @@
         <v>324772.0</v>
       </c>
       <c r="R4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -2221,42 +2371,48 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X4" t="n">
+        <v>0.041722</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.00684234693877551</v>
+      </c>
+      <c r="Z4" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z4" t="e">
+      <c r="AA4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" t="s">
         <v>40</v>
       </c>
-      <c r="E5" t="s">
-        <v>38</v>
-      </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>0.066314</v>
+        <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
         <v>1.2840162794139224E-4</v>
@@ -2268,16 +2424,16 @@
         <v>0.0715086275910485</v>
       </c>
       <c r="K5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O5" t="n">
         <v>0.03729307887593385</v>
@@ -2289,7 +2445,7 @@
         <v>324772.0</v>
       </c>
       <c r="R5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -2301,42 +2457,48 @@
         <v>0.0114775510204082</v>
       </c>
       <c r="V5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X5" t="n">
+        <v>-0.080535</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.0282632653061224</v>
+      </c>
+      <c r="Z5" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y5" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z5" t="e">
+      <c r="AA5" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" t="s">
         <v>40</v>
       </c>
-      <c r="E6" t="s">
-        <v>38</v>
-      </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>0.036955</v>
+        <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
         <v>-0.02411519209693045</v>
@@ -2348,16 +2510,16 @@
         <v>0.2552929439730026</v>
       </c>
       <c r="K6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O6" t="n">
         <v>0.026102962666304047</v>
@@ -2369,7 +2531,7 @@
         <v>324772.0</v>
       </c>
       <c r="R6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -2381,42 +2543,48 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X6" t="n">
+        <v>-0.036955</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.00718163265306122</v>
+      </c>
+      <c r="Z6" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z6" t="e">
+      <c r="AA6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
         <v>39</v>
       </c>
-      <c r="E7" t="s">
-        <v>37</v>
-      </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>0.060792</v>
+        <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
         <v>-0.02576140061176619</v>
@@ -2428,16 +2596,16 @@
         <v>0.07838883893931743</v>
       </c>
       <c r="K7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O7" t="n">
         <v>0.036227973091514154</v>
@@ -2449,7 +2617,7 @@
         <v>324772.0</v>
       </c>
       <c r="R7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -2461,18 +2629,24 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="V7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X7" t="n">
+        <v>-0.071191</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.0245357142857143</v>
+      </c>
+      <c r="Z7" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y7" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z7" t="e">
+      <c r="AA7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2563,28 +2737,34 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
+      <c r="AA1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" t="s">
         <v>39</v>
       </c>
-      <c r="E2" t="s">
-        <v>37</v>
-      </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.063746</v>
+        <v>0.063746</v>
       </c>
       <c r="H2" t="n">
         <v>0.013211324428284068</v>
@@ -2596,16 +2776,16 @@
         <v>0.3861255363839027</v>
       </c>
       <c r="K2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O2" t="n">
         <v>0.012029158076366281</v>
@@ -2617,7 +2797,7 @@
         <v>232809.0</v>
       </c>
       <c r="R2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -2629,42 +2809,48 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X2" t="n">
+        <v>0.063746</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.0113683673469388</v>
+      </c>
+      <c r="Z2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z2" t="e">
+      <c r="AA2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" t="s">
         <v>39</v>
       </c>
-      <c r="E3" t="s">
-        <v>37</v>
-      </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>0.039983</v>
+        <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
         <v>-7.043450094299762E-4</v>
@@ -2676,16 +2862,16 @@
         <v>0.2856375827394989</v>
       </c>
       <c r="K3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O3" t="n">
         <v>0.010153915923388946</v>
@@ -2697,7 +2883,7 @@
         <v>232809.0</v>
       </c>
       <c r="R3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -2709,42 +2895,48 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="V3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X3" t="n">
+        <v>-0.042572</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.0144209183673469</v>
+      </c>
+      <c r="Z3" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z3" t="e">
+      <c r="AA3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" t="s">
         <v>40</v>
       </c>
-      <c r="E4" t="s">
-        <v>38</v>
-      </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H4" t="n">
         <v>-0.004470800376588844</v>
@@ -2756,16 +2948,16 @@
         <v>0.41616088725092243</v>
       </c>
       <c r="K4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O4" t="n">
         <v>0.013443474169917223</v>
@@ -2777,7 +2969,7 @@
         <v>232809.0</v>
       </c>
       <c r="R4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -2789,42 +2981,48 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X4" t="n">
+        <v>0.041722</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.00684234693877551</v>
+      </c>
+      <c r="Z4" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z4" t="e">
+      <c r="AA4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" t="s">
         <v>40</v>
       </c>
-      <c r="E5" t="s">
-        <v>38</v>
-      </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>0.066314</v>
+        <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
         <v>0.02100408358834647</v>
@@ -2836,16 +3034,16 @@
         <v>0.07129878999523215</v>
       </c>
       <c r="K5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O5" t="n">
         <v>0.014270943913311256</v>
@@ -2857,7 +3055,7 @@
         <v>232809.0</v>
       </c>
       <c r="R5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -2869,42 +3067,48 @@
         <v>0.0114775510204082</v>
       </c>
       <c r="V5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X5" t="n">
+        <v>-0.080535</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.0282632653061224</v>
+      </c>
+      <c r="Z5" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y5" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z5" t="e">
+      <c r="AA5" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" t="s">
         <v>40</v>
       </c>
-      <c r="E6" t="s">
-        <v>38</v>
-      </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>0.036955</v>
+        <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
         <v>-0.0075008896559969965</v>
@@ -2916,16 +3120,16 @@
         <v>0.2553939065929582</v>
       </c>
       <c r="K6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O6" t="n">
         <v>0.010051400112843665</v>
@@ -2937,7 +3141,7 @@
         <v>232809.0</v>
       </c>
       <c r="R6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -2949,42 +3153,48 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X6" t="n">
+        <v>-0.036955</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.00718163265306122</v>
+      </c>
+      <c r="Z6" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z6" t="e">
+      <c r="AA6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
         <v>39</v>
       </c>
-      <c r="E7" t="s">
-        <v>37</v>
-      </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>0.060792</v>
+        <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
         <v>0.020498030949925836</v>
@@ -2996,16 +3206,16 @@
         <v>0.07822506861848125</v>
       </c>
       <c r="K7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O7" t="n">
         <v>0.013739531362455648</v>
@@ -3017,7 +3227,7 @@
         <v>232809.0</v>
       </c>
       <c r="R7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -3029,18 +3239,24 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="V7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X7" t="n">
+        <v>-0.071191</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.0245357142857143</v>
+      </c>
+      <c r="Z7" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y7" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z7" t="e">
+      <c r="AA7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -3131,28 +3347,34 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
+      <c r="AA1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" t="s">
         <v>39</v>
       </c>
-      <c r="E2" t="s">
-        <v>37</v>
-      </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.063746</v>
+        <v>0.063746</v>
       </c>
       <c r="H2" t="n">
         <v>-0.02541077373875312</v>
@@ -3164,16 +3386,16 @@
         <v>0.3863387461620198</v>
       </c>
       <c r="K2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O2" t="n">
         <v>0.021726510957283177</v>
@@ -3185,7 +3407,7 @@
         <v>306802.0</v>
       </c>
       <c r="R2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -3197,42 +3419,48 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X2" t="n">
+        <v>0.063746</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.0113683673469388</v>
+      </c>
+      <c r="Z2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z2" t="e">
+      <c r="AA2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" t="s">
         <v>39</v>
       </c>
-      <c r="E3" t="s">
-        <v>37</v>
-      </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>0.039983</v>
+        <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
         <v>0.01321523652819153</v>
@@ -3244,16 +3472,16 @@
         <v>0.28551639167932413</v>
       </c>
       <c r="K3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O3" t="n">
         <v>0.018533218618133722</v>
@@ -3265,7 +3493,7 @@
         <v>306802.0</v>
       </c>
       <c r="R3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -3277,42 +3505,48 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="V3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X3" t="n">
+        <v>-0.042572</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.0144209183673469</v>
+      </c>
+      <c r="Z3" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z3" t="e">
+      <c r="AA3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" t="s">
         <v>40</v>
       </c>
-      <c r="E4" t="s">
-        <v>38</v>
-      </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H4" t="n">
         <v>-0.03237005824445815</v>
@@ -3324,16 +3558,16 @@
         <v>0.41629943742218106</v>
       </c>
       <c r="K4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O4" t="n">
         <v>0.02429420763830611</v>
@@ -3345,7 +3579,7 @@
         <v>306802.0</v>
       </c>
       <c r="R4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -3357,42 +3591,48 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X4" t="n">
+        <v>0.041722</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.00684234693877551</v>
+      </c>
+      <c r="Z4" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z4" t="e">
+      <c r="AA4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" t="s">
         <v>40</v>
       </c>
-      <c r="E5" t="s">
-        <v>38</v>
-      </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>0.066314</v>
+        <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
         <v>0.018808687601383066</v>
@@ -3404,16 +3644,16 @@
         <v>0.07141250708926278</v>
       </c>
       <c r="K5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O5" t="n">
         <v>0.026019190793507396</v>
@@ -3425,7 +3665,7 @@
         <v>306802.0</v>
       </c>
       <c r="R5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -3437,42 +3677,48 @@
         <v>0.0114775510204082</v>
       </c>
       <c r="V5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X5" t="n">
+        <v>-0.080535</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.0282632653061224</v>
+      </c>
+      <c r="Z5" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y5" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z5" t="e">
+      <c r="AA5" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" t="s">
         <v>40</v>
       </c>
-      <c r="E6" t="s">
-        <v>38</v>
-      </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>0.036955</v>
+        <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
         <v>0.026755660901255824</v>
@@ -3484,16 +3730,16 @@
         <v>0.2553177619441855</v>
       </c>
       <c r="K6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O6" t="n">
         <v>0.018336926204178518</v>
@@ -3505,7 +3751,7 @@
         <v>306802.0</v>
       </c>
       <c r="R6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -3517,42 +3763,48 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X6" t="n">
+        <v>-0.036955</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.00718163265306122</v>
+      </c>
+      <c r="Z6" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z6" t="e">
+      <c r="AA6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
         <v>39</v>
       </c>
-      <c r="E7" t="s">
-        <v>37</v>
-      </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>0.060792</v>
+        <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
         <v>2.6091172210830654E-4</v>
@@ -3564,16 +3816,16 @@
         <v>0.07829968513894955</v>
       </c>
       <c r="K7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O7" t="n">
         <v>0.02521583489929918</v>
@@ -3585,7 +3837,7 @@
         <v>306802.0</v>
       </c>
       <c r="R7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -3597,18 +3849,24 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="V7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X7" t="n">
+        <v>-0.071191</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.0245357142857143</v>
+      </c>
+      <c r="Z7" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y7" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z7" t="e">
+      <c r="AA7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB7" t="e">
         <v>#N/A</v>
       </c>
     </row>

--- a/MR_UKBiobank/BinaryData/SA_Enrolment/gMR_dat.xlsx
+++ b/MR_UKBiobank/BinaryData/SA_Enrolment/gMR_dat.xlsx
@@ -64,10 +64,16 @@
     <t>p.outcome</t>
   </si>
   <si>
+    <t>outcome</t>
+  </si>
+  <si>
     <t>n.outcome</t>
   </si>
   <si>
-    <t>outcome</t>
+    <t>cases.outcome</t>
+  </si>
+  <si>
+    <t>controls.outcome</t>
   </si>
   <si>
     <t>pval.exposure</t>
@@ -83,12 +89,6 @@
   </si>
   <si>
     <t>exposure</t>
-  </si>
-  <si>
-    <t>beta.exposure_corrected</t>
-  </si>
-  <si>
-    <t>se.exposure_corrected</t>
   </si>
   <si>
     <t>action</t>
@@ -327,13 +327,13 @@
         <v>0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>0.11320797341461863</v>
+        <v>0.143541354627436</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3861253893094979</v>
+        <v>0.5420766304694307</v>
       </c>
       <c r="K2" t="s">
         <v>43</v>
@@ -348,37 +348,37 @@
         <v>44</v>
       </c>
       <c r="O2" t="n">
-        <v>0.03974158279313367</v>
+        <v>0.04685689457839827</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0043911701345451274</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>315944.0</v>
-      </c>
-      <c r="R2" t="s">
+        <v>0.00218838208738476</v>
+      </c>
+      <c r="Q2" t="s">
         <v>44</v>
       </c>
+      <c r="R2" t="n">
+        <v>235285.0</v>
+      </c>
       <c r="S2" t="n">
+        <v>2796.0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>232489.0</v>
+      </c>
+      <c r="U2" t="n">
         <v>2.1E-8</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>14009.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>0.0113683673469388</v>
       </c>
-      <c r="V2" t="s">
-        <v>45</v>
-      </c>
-      <c r="W2" t="s">
-        <v>45</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.063746</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.0113683673469388</v>
+      <c r="X2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>45</v>
       </c>
       <c r="Z2" t="n">
         <v>2.0</v>
@@ -413,13 +413,13 @@
         <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.06923308600316334</v>
+        <v>-0.07127417299891287</v>
       </c>
       <c r="I3" t="n">
         <v>0.3171</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2859114273415542</v>
+        <v>0.34758696899504854</v>
       </c>
       <c r="K3" t="s">
         <v>43</v>
@@ -434,37 +434,37 @@
         <v>44</v>
       </c>
       <c r="O3" t="n">
-        <v>0.03254520177317449</v>
+        <v>0.038056525349821166</v>
       </c>
       <c r="P3" t="n">
-        <v>0.03339598562502328</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>315944.0</v>
-      </c>
-      <c r="R3" t="s">
+        <v>0.06108906680187869</v>
+      </c>
+      <c r="Q3" t="s">
         <v>44</v>
       </c>
+      <c r="R3" t="n">
+        <v>235285.0</v>
+      </c>
       <c r="S3" t="n">
+        <v>2796.0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>232489.0</v>
+      </c>
+      <c r="U3" t="n">
         <v>8.03E-9</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>49371.0</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.0069265306122449</v>
       </c>
-      <c r="V3" t="s">
-        <v>45</v>
-      </c>
-      <c r="W3" t="s">
-        <v>45</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-0.042572</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.0144209183673469</v>
+      <c r="X3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>45</v>
       </c>
       <c r="Z3" t="n">
         <v>2.0</v>
@@ -499,13 +499,13 @@
         <v>0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>0.15891464551332074</v>
+        <v>0.1876745017401533</v>
       </c>
       <c r="I4" t="n">
         <v>0.6699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.41606265667333453</v>
+        <v>0.6015279342074505</v>
       </c>
       <c r="K4" t="s">
         <v>43</v>
@@ -520,37 +520,37 @@
         <v>44</v>
       </c>
       <c r="O4" t="n">
-        <v>0.045606863996996046</v>
+        <v>0.053959776377508505</v>
       </c>
       <c r="P4" t="n">
-        <v>4.93157339966776E-4</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>315944.0</v>
-      </c>
-      <c r="R4" t="s">
+        <v>5.050861259054416E-4</v>
+      </c>
+      <c r="Q4" t="s">
         <v>44</v>
       </c>
+      <c r="R4" t="n">
+        <v>235285.0</v>
+      </c>
       <c r="S4" t="n">
+        <v>2796.0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>232489.0</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V4" t="s">
-        <v>45</v>
-      </c>
-      <c r="W4" t="s">
-        <v>45</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.041722</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.00684234693877551</v>
+      <c r="X4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>45</v>
       </c>
       <c r="Z4" t="n">
         <v>2.0</v>
@@ -585,13 +585,13 @@
         <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.10397134179674575</v>
+        <v>-0.11758967567121484</v>
       </c>
       <c r="I5" t="n">
         <v>0.0882</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07170574532195578</v>
+        <v>0.07404211913211636</v>
       </c>
       <c r="K5" t="s">
         <v>43</v>
@@ -606,37 +606,37 @@
         <v>44</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04796820226881708</v>
+        <v>0.056536245275241</v>
       </c>
       <c r="P5" t="n">
-        <v>0.030196331482093285</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>315944.0</v>
-      </c>
-      <c r="R5" t="s">
+        <v>0.03753480482377513</v>
+      </c>
+      <c r="Q5" t="s">
         <v>44</v>
       </c>
+      <c r="R5" t="n">
+        <v>235285.0</v>
+      </c>
       <c r="S5" t="n">
+        <v>2796.0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>232489.0</v>
+      </c>
+      <c r="U5" t="n">
         <v>7.76E-9</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>0.0114775510204082</v>
       </c>
-      <c r="V5" t="s">
-        <v>45</v>
-      </c>
-      <c r="W5" t="s">
-        <v>45</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-0.080535</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.0282632653061224</v>
+      <c r="X5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>45</v>
       </c>
       <c r="Z5" t="n">
         <v>2.0</v>
@@ -671,13 +671,13 @@
         <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.03545339169759979</v>
+        <v>-0.04790190096151197</v>
       </c>
       <c r="I6" t="n">
         <v>0.2786</v>
       </c>
       <c r="J6" t="n">
-        <v>0.25553104347605904</v>
+        <v>0.3025819750515332</v>
       </c>
       <c r="K6" t="s">
         <v>43</v>
@@ -692,37 +692,37 @@
         <v>44</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03233695930566997</v>
+        <v>0.03782663779517823</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2729152688696306</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>315944.0</v>
-      </c>
-      <c r="R6" t="s">
+        <v>0.2053864960360948</v>
+      </c>
+      <c r="Q6" t="s">
         <v>44</v>
       </c>
+      <c r="R6" t="n">
+        <v>235285.0</v>
+      </c>
       <c r="S6" t="n">
+        <v>2796.0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>232489.0</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.72E-7</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.00718163265306122</v>
       </c>
-      <c r="V6" t="s">
-        <v>45</v>
-      </c>
-      <c r="W6" t="s">
-        <v>45</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.036955</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.00718163265306122</v>
+      <c r="X6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>45</v>
       </c>
       <c r="Z6" t="n">
         <v>2.0</v>
@@ -757,13 +757,13 @@
         <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.11333008059645083</v>
+        <v>-0.10645415053794371</v>
       </c>
       <c r="I7" t="n">
         <v>0.0886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07857879877446636</v>
+        <v>0.08146503176998109</v>
       </c>
       <c r="K7" t="s">
         <v>43</v>
@@ -778,37 +778,37 @@
         <v>44</v>
       </c>
       <c r="O7" t="n">
-        <v>0.046260637728663574</v>
+        <v>0.054073542697412116</v>
       </c>
       <c r="P7" t="n">
-        <v>0.014292897420276379</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>315944.0</v>
-      </c>
-      <c r="R7" t="s">
+        <v>0.048988471344196934</v>
+      </c>
+      <c r="Q7" t="s">
         <v>44</v>
       </c>
+      <c r="R7" t="n">
+        <v>235285.0</v>
+      </c>
       <c r="S7" t="n">
+        <v>2796.0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>232489.0</v>
+      </c>
+      <c r="U7" t="n">
         <v>9.54E-8</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.0113857142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>45</v>
-      </c>
-      <c r="W7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.071191</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.0245357142857143</v>
+      <c r="X7" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>45</v>
       </c>
       <c r="Z7" t="n">
         <v>2.0</v>
@@ -937,13 +937,13 @@
         <v>0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.00640896296765077</v>
+        <v>-0.023743254474032728</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.38630181408322994</v>
+        <v>0.5425642455268893</v>
       </c>
       <c r="K2" t="s">
         <v>43</v>
@@ -958,37 +958,37 @@
         <v>47</v>
       </c>
       <c r="O2" t="n">
-        <v>0.017743298151836128</v>
+        <v>0.02054434513782966</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7179464170298148</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>317626.0</v>
-      </c>
-      <c r="R2" t="s">
+        <v>0.24780080512421515</v>
+      </c>
+      <c r="Q2" t="s">
         <v>47</v>
       </c>
+      <c r="R2" t="n">
+        <v>236748.0</v>
+      </c>
       <c r="S2" t="n">
+        <v>13341.0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>223407.0</v>
+      </c>
+      <c r="U2" t="n">
         <v>2.1E-8</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>14009.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>0.0113683673469388</v>
       </c>
-      <c r="V2" t="s">
-        <v>45</v>
-      </c>
-      <c r="W2" t="s">
-        <v>45</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.063746</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.0113683673469388</v>
+      <c r="X2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>45</v>
       </c>
       <c r="Z2" t="n">
         <v>2.0</v>
@@ -1023,13 +1023,13 @@
         <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>0.024098274429378872</v>
+        <v>0.007427470369346498</v>
       </c>
       <c r="I3" t="n">
         <v>0.3171</v>
       </c>
       <c r="J3" t="n">
-        <v>0.28552133641452526</v>
+        <v>0.3471475999797253</v>
       </c>
       <c r="K3" t="s">
         <v>43</v>
@@ -1044,37 +1044,37 @@
         <v>47</v>
       </c>
       <c r="O3" t="n">
-        <v>0.015073566416373536</v>
+        <v>0.017502991442480798</v>
       </c>
       <c r="P3" t="n">
-        <v>0.10988486194855365</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>317626.0</v>
-      </c>
-      <c r="R3" t="s">
+        <v>0.6713074154431464</v>
+      </c>
+      <c r="Q3" t="s">
         <v>47</v>
       </c>
+      <c r="R3" t="n">
+        <v>236748.0</v>
+      </c>
       <c r="S3" t="n">
+        <v>13341.0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>223407.0</v>
+      </c>
+      <c r="U3" t="n">
         <v>8.03E-9</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>49371.0</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.0069265306122449</v>
       </c>
-      <c r="V3" t="s">
-        <v>45</v>
-      </c>
-      <c r="W3" t="s">
-        <v>45</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-0.042572</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.0144209183673469</v>
+      <c r="X3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>45</v>
       </c>
       <c r="Z3" t="n">
         <v>2.0</v>
@@ -1109,13 +1109,13 @@
         <v>0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.016300450396919127</v>
+        <v>-0.03256545567730134</v>
       </c>
       <c r="I4" t="n">
         <v>0.6699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4161702757330949</v>
+        <v>0.6019522868197408</v>
       </c>
       <c r="K4" t="s">
         <v>43</v>
@@ -1130,37 +1130,37 @@
         <v>47</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01983774514641621</v>
+        <v>0.022957985618616</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4112541099419501</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>317626.0</v>
-      </c>
-      <c r="R4" t="s">
+        <v>0.15605051823215044</v>
+      </c>
+      <c r="Q4" t="s">
         <v>47</v>
       </c>
+      <c r="R4" t="n">
+        <v>236748.0</v>
+      </c>
       <c r="S4" t="n">
+        <v>13341.0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>223407.0</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V4" t="s">
-        <v>45</v>
-      </c>
-      <c r="W4" t="s">
-        <v>45</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.041722</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.00684234693877551</v>
+      <c r="X4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>45</v>
       </c>
       <c r="Z4" t="n">
         <v>2.0</v>
@@ -1195,13 +1195,13 @@
         <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>0.031915254592675156</v>
+        <v>0.0455211694594714</v>
       </c>
       <c r="I5" t="n">
         <v>0.0882</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07146770100684453</v>
+        <v>0.07389925152482808</v>
       </c>
       <c r="K5" t="s">
         <v>43</v>
@@ -1216,37 +1216,37 @@
         <v>47</v>
       </c>
       <c r="O5" t="n">
-        <v>0.021046780336491662</v>
+        <v>0.024416385079967885</v>
       </c>
       <c r="P5" t="n">
-        <v>0.12941923696645752</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>317626.0</v>
-      </c>
-      <c r="R5" t="s">
+        <v>0.062269799538431835</v>
+      </c>
+      <c r="Q5" t="s">
         <v>47</v>
       </c>
+      <c r="R5" t="n">
+        <v>236748.0</v>
+      </c>
       <c r="S5" t="n">
+        <v>13341.0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>223407.0</v>
+      </c>
+      <c r="U5" t="n">
         <v>7.76E-9</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>0.0114775510204082</v>
       </c>
-      <c r="V5" t="s">
-        <v>45</v>
-      </c>
-      <c r="W5" t="s">
-        <v>45</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-0.080535</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.0282632653061224</v>
+      <c r="X5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>45</v>
       </c>
       <c r="Z5" t="n">
         <v>2.0</v>
@@ -1281,13 +1281,13 @@
         <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>0.023647811168193016</v>
+        <v>0.027816934421720615</v>
       </c>
       <c r="I6" t="n">
         <v>0.2786</v>
       </c>
       <c r="J6" t="n">
-        <v>0.25517432452003297</v>
+        <v>0.30219685065977325</v>
       </c>
       <c r="K6" t="s">
         <v>43</v>
@@ -1302,37 +1302,37 @@
         <v>47</v>
       </c>
       <c r="O6" t="n">
-        <v>0.014901044887753442</v>
+        <v>0.017325839505166283</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1125148799805218</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>317626.0</v>
-      </c>
-      <c r="R6" t="s">
+        <v>0.10838001719155078</v>
+      </c>
+      <c r="Q6" t="s">
         <v>47</v>
       </c>
+      <c r="R6" t="n">
+        <v>236748.0</v>
+      </c>
       <c r="S6" t="n">
+        <v>13341.0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>223407.0</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.72E-7</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.00718163265306122</v>
       </c>
-      <c r="V6" t="s">
-        <v>45</v>
-      </c>
-      <c r="W6" t="s">
-        <v>45</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.036955</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.00718163265306122</v>
+      <c r="X6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>45</v>
       </c>
       <c r="Z6" t="n">
         <v>2.0</v>
@@ -1367,13 +1367,13 @@
         <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>0.024445683935007102</v>
+        <v>0.03552595405391902</v>
       </c>
       <c r="I7" t="n">
         <v>0.0886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07834528659492611</v>
+        <v>0.08128262963150693</v>
       </c>
       <c r="K7" t="s">
         <v>43</v>
@@ -1388,37 +1388,37 @@
         <v>47</v>
       </c>
       <c r="O7" t="n">
-        <v>0.020318004866706867</v>
+        <v>0.023589749148672155</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2289168251240264</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>317626.0</v>
-      </c>
-      <c r="R7" t="s">
+        <v>0.1320694389766612</v>
+      </c>
+      <c r="Q7" t="s">
         <v>47</v>
       </c>
+      <c r="R7" t="n">
+        <v>236748.0</v>
+      </c>
       <c r="S7" t="n">
+        <v>13341.0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>223407.0</v>
+      </c>
+      <c r="U7" t="n">
         <v>9.54E-8</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.0113857142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>45</v>
-      </c>
-      <c r="W7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.071191</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.0245357142857143</v>
+      <c r="X7" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>45</v>
       </c>
       <c r="Z7" t="n">
         <v>2.0</v>
@@ -1547,13 +1547,13 @@
         <v>0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.01101993481684144</v>
+        <v>-0.033922920546200365</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3862300865964806</v>
+        <v>0.5425711988489695</v>
       </c>
       <c r="K2" t="s">
         <v>43</v>
@@ -1568,37 +1568,37 @@
         <v>48</v>
       </c>
       <c r="O2" t="n">
-        <v>0.02679158993325966</v>
+        <v>0.031180999242138966</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6808374123883479</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>316872.0</v>
-      </c>
-      <c r="R2" t="s">
+        <v>0.276623518475872</v>
+      </c>
+      <c r="Q2" t="s">
         <v>48</v>
       </c>
+      <c r="R2" t="n">
+        <v>236310.0</v>
+      </c>
       <c r="S2" t="n">
+        <v>5760.0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>230550.0</v>
+      </c>
+      <c r="U2" t="n">
         <v>2.1E-8</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>14009.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>0.0113683673469388</v>
       </c>
-      <c r="V2" t="s">
-        <v>45</v>
-      </c>
-      <c r="W2" t="s">
-        <v>45</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.063746</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.0113683673469388</v>
+      <c r="X2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>45</v>
       </c>
       <c r="Z2" t="n">
         <v>2.0</v>
@@ -1633,13 +1633,13 @@
         <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>0.021137580129547143</v>
+        <v>0.004691762576901919</v>
       </c>
       <c r="I3" t="n">
         <v>0.3171</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2854528011310561</v>
+        <v>0.3471181922051542</v>
       </c>
       <c r="K3" t="s">
         <v>43</v>
@@ -1654,37 +1654,37 @@
         <v>48</v>
       </c>
       <c r="O3" t="n">
-        <v>0.022792438480451423</v>
+        <v>0.02663280500303198</v>
       </c>
       <c r="P3" t="n">
-        <v>0.35372178983942304</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>316872.0</v>
-      </c>
-      <c r="R3" t="s">
+        <v>0.8601644793993011</v>
+      </c>
+      <c r="Q3" t="s">
         <v>48</v>
       </c>
+      <c r="R3" t="n">
+        <v>236310.0</v>
+      </c>
       <c r="S3" t="n">
+        <v>5760.0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>230550.0</v>
+      </c>
+      <c r="U3" t="n">
         <v>8.03E-9</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>49371.0</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.0069265306122449</v>
       </c>
-      <c r="V3" t="s">
-        <v>45</v>
-      </c>
-      <c r="W3" t="s">
-        <v>45</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-0.042572</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.0144209183673469</v>
+      <c r="X3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>45</v>
       </c>
       <c r="Z3" t="n">
         <v>2.0</v>
@@ -1719,13 +1719,13 @@
         <v>0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.025141604942097516</v>
+        <v>-0.043351908989276426</v>
       </c>
       <c r="I4" t="n">
         <v>0.6699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.41618224393445935</v>
+        <v>0.6019910287334433</v>
       </c>
       <c r="K4" t="s">
         <v>43</v>
@@ -1740,37 +1740,37 @@
         <v>48</v>
       </c>
       <c r="O4" t="n">
-        <v>0.029897604744285104</v>
+        <v>0.03481577994158205</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4003906702027964</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>316872.0</v>
-      </c>
-      <c r="R4" t="s">
+        <v>0.21306563349644525</v>
+      </c>
+      <c r="Q4" t="s">
         <v>48</v>
       </c>
+      <c r="R4" t="n">
+        <v>236310.0</v>
+      </c>
       <c r="S4" t="n">
+        <v>5760.0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>230550.0</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V4" t="s">
-        <v>45</v>
-      </c>
-      <c r="W4" t="s">
-        <v>45</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.041722</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.00684234693877551</v>
+      <c r="X4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>45</v>
       </c>
       <c r="Z4" t="n">
         <v>2.0</v>
@@ -1805,13 +1805,13 @@
         <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>0.023390982754306833</v>
+        <v>0.031161522754317803</v>
       </c>
       <c r="I5" t="n">
         <v>0.0882</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07156044080890707</v>
+        <v>0.07397274766196944</v>
       </c>
       <c r="K5" t="s">
         <v>43</v>
@@ -1826,37 +1826,37 @@
         <v>48</v>
       </c>
       <c r="O5" t="n">
-        <v>0.03188592316010013</v>
+        <v>0.03731756443810384</v>
       </c>
       <c r="P5" t="n">
-        <v>0.46320270349997084</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>316872.0</v>
-      </c>
-      <c r="R5" t="s">
+        <v>0.40369724285190645</v>
+      </c>
+      <c r="Q5" t="s">
         <v>48</v>
       </c>
+      <c r="R5" t="n">
+        <v>236310.0</v>
+      </c>
       <c r="S5" t="n">
+        <v>5760.0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>230550.0</v>
+      </c>
+      <c r="U5" t="n">
         <v>7.76E-9</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>0.0114775510204082</v>
       </c>
-      <c r="V5" t="s">
-        <v>45</v>
-      </c>
-      <c r="W5" t="s">
-        <v>45</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-0.080535</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.0282632653061224</v>
+      <c r="X5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>45</v>
       </c>
       <c r="Z5" t="n">
         <v>2.0</v>
@@ -1891,13 +1891,13 @@
         <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007619934041396579</v>
+        <v>0.010313915513288646</v>
       </c>
       <c r="I6" t="n">
         <v>0.2786</v>
       </c>
       <c r="J6" t="n">
-        <v>0.25519768234492163</v>
+        <v>0.3021560661842495</v>
       </c>
       <c r="K6" t="s">
         <v>43</v>
@@ -1912,37 +1912,37 @@
         <v>48</v>
       </c>
       <c r="O6" t="n">
-        <v>0.022530111984744857</v>
+        <v>0.026361544463311275</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7352041088365866</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>316872.0</v>
-      </c>
-      <c r="R6" t="s">
+        <v>0.6956135398762116</v>
+      </c>
+      <c r="Q6" t="s">
         <v>48</v>
       </c>
+      <c r="R6" t="n">
+        <v>236310.0</v>
+      </c>
       <c r="S6" t="n">
+        <v>5760.0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>230550.0</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.72E-7</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.00718163265306122</v>
       </c>
-      <c r="V6" t="s">
-        <v>45</v>
-      </c>
-      <c r="W6" t="s">
-        <v>45</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.036955</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.00718163265306122</v>
+      <c r="X6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>45</v>
       </c>
       <c r="Z6" t="n">
         <v>2.0</v>
@@ -1977,13 +1977,13 @@
         <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02604819288088866</v>
+        <v>0.016682128142619487</v>
       </c>
       <c r="I7" t="n">
         <v>0.0886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07841336564922113</v>
+        <v>0.08132326181710466</v>
       </c>
       <c r="K7" t="s">
         <v>43</v>
@@ -1998,37 +1998,37 @@
         <v>48</v>
       </c>
       <c r="O7" t="n">
-        <v>0.03069748009021115</v>
+        <v>0.03612938020672069</v>
       </c>
       <c r="P7" t="n">
-        <v>0.39613452897951684</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>316872.0</v>
-      </c>
-      <c r="R7" t="s">
+        <v>0.6442727825751234</v>
+      </c>
+      <c r="Q7" t="s">
         <v>48</v>
       </c>
+      <c r="R7" t="n">
+        <v>236310.0</v>
+      </c>
       <c r="S7" t="n">
+        <v>5760.0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>230550.0</v>
+      </c>
+      <c r="U7" t="n">
         <v>9.54E-8</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.0113857142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>45</v>
-      </c>
-      <c r="W7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.071191</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.0245357142857143</v>
+      <c r="X7" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>45</v>
       </c>
       <c r="Z7" t="n">
         <v>2.0</v>
@@ -2157,13 +2157,13 @@
         <v>0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>0.014914633384528763</v>
+        <v>0.00295395513523222</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.38618630916458313</v>
+        <v>0.5424455762346113</v>
       </c>
       <c r="K2" t="s">
         <v>43</v>
@@ -2178,37 +2178,37 @@
         <v>49</v>
       </c>
       <c r="O2" t="n">
-        <v>0.03126456969611048</v>
+        <v>0.03664526398997029</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6333294692076733</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>324772.0</v>
-      </c>
-      <c r="R2" t="s">
+        <v>0.935752538500844</v>
+      </c>
+      <c r="Q2" t="s">
         <v>49</v>
       </c>
+      <c r="R2" t="n">
+        <v>241898.0</v>
+      </c>
       <c r="S2" t="n">
+        <v>4251.0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>237647.0</v>
+      </c>
+      <c r="U2" t="n">
         <v>2.1E-8</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>14009.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>0.0113683673469388</v>
       </c>
-      <c r="V2" t="s">
-        <v>45</v>
-      </c>
-      <c r="W2" t="s">
-        <v>45</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.063746</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.0113683673469388</v>
+      <c r="X2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>45</v>
       </c>
       <c r="Z2" t="n">
         <v>2.0</v>
@@ -2243,13 +2243,13 @@
         <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0244839522940332</v>
+        <v>-0.022733280360683374</v>
       </c>
       <c r="I3" t="n">
         <v>0.3171</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2855695688051926</v>
+        <v>0.34720626048995856</v>
       </c>
       <c r="K3" t="s">
         <v>43</v>
@@ -2264,37 +2264,37 @@
         <v>49</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02632983385451268</v>
+        <v>0.030944162358105667</v>
       </c>
       <c r="P3" t="n">
-        <v>0.35242601369364845</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>324772.0</v>
-      </c>
-      <c r="R3" t="s">
+        <v>0.46254969644066457</v>
+      </c>
+      <c r="Q3" t="s">
         <v>49</v>
       </c>
+      <c r="R3" t="n">
+        <v>241898.0</v>
+      </c>
       <c r="S3" t="n">
+        <v>4251.0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>237647.0</v>
+      </c>
+      <c r="U3" t="n">
         <v>8.03E-9</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>49371.0</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.0069265306122449</v>
       </c>
-      <c r="V3" t="s">
-        <v>45</v>
-      </c>
-      <c r="W3" t="s">
-        <v>45</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-0.042572</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.0144209183673469</v>
+      <c r="X3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>45</v>
       </c>
       <c r="Z3" t="n">
         <v>2.0</v>
@@ -2329,13 +2329,13 @@
         <v>0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00197716985396096</v>
+        <v>0.022349519218333835</v>
       </c>
       <c r="I4" t="n">
         <v>0.6699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4161303930141761</v>
+        <v>0.6018797178976263</v>
       </c>
       <c r="K4" t="s">
         <v>43</v>
@@ -2350,37 +2350,37 @@
         <v>49</v>
       </c>
       <c r="O4" t="n">
-        <v>0.034957411930060966</v>
+        <v>0.041404230393366034</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9548961857456228</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>324772.0</v>
-      </c>
-      <c r="R4" t="s">
+        <v>0.5893430353599408</v>
+      </c>
+      <c r="Q4" t="s">
         <v>49</v>
       </c>
+      <c r="R4" t="n">
+        <v>241898.0</v>
+      </c>
       <c r="S4" t="n">
+        <v>4251.0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>237647.0</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V4" t="s">
-        <v>45</v>
-      </c>
-      <c r="W4" t="s">
-        <v>45</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.041722</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.00684234693877551</v>
+      <c r="X4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>45</v>
       </c>
       <c r="Z4" t="n">
         <v>2.0</v>
@@ -2415,13 +2415,13 @@
         <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2840162794139224E-4</v>
+        <v>0.03146645366611186</v>
       </c>
       <c r="I5" t="n">
         <v>0.0882</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0715086275910485</v>
+        <v>0.07389064812441608</v>
       </c>
       <c r="K5" t="s">
         <v>43</v>
@@ -2436,37 +2436,37 @@
         <v>49</v>
       </c>
       <c r="O5" t="n">
-        <v>0.03729307887593385</v>
+        <v>0.04345869753093335</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9972528555649158</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>324772.0</v>
-      </c>
-      <c r="R5" t="s">
+        <v>0.469032444042594</v>
+      </c>
+      <c r="Q5" t="s">
         <v>49</v>
       </c>
+      <c r="R5" t="n">
+        <v>241898.0</v>
+      </c>
       <c r="S5" t="n">
+        <v>4251.0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>237647.0</v>
+      </c>
+      <c r="U5" t="n">
         <v>7.76E-9</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>0.0114775510204082</v>
       </c>
-      <c r="V5" t="s">
-        <v>45</v>
-      </c>
-      <c r="W5" t="s">
-        <v>45</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-0.080535</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.0282632653061224</v>
+      <c r="X5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>45</v>
       </c>
       <c r="Z5" t="n">
         <v>2.0</v>
@@ -2501,13 +2501,13 @@
         <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.02411519209693045</v>
+        <v>0.005813122755726773</v>
       </c>
       <c r="I6" t="n">
         <v>0.2786</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2552929439730026</v>
+        <v>0.30234437655540763</v>
       </c>
       <c r="K6" t="s">
         <v>43</v>
@@ -2522,37 +2522,37 @@
         <v>49</v>
       </c>
       <c r="O6" t="n">
-        <v>0.026102962666304047</v>
+        <v>0.03068483439155711</v>
       </c>
       <c r="P6" t="n">
-        <v>0.35556501625694814</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>324772.0</v>
-      </c>
-      <c r="R6" t="s">
+        <v>0.8497431819282618</v>
+      </c>
+      <c r="Q6" t="s">
         <v>49</v>
       </c>
+      <c r="R6" t="n">
+        <v>241898.0</v>
+      </c>
       <c r="S6" t="n">
+        <v>4251.0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>237647.0</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.72E-7</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.00718163265306122</v>
       </c>
-      <c r="V6" t="s">
-        <v>45</v>
-      </c>
-      <c r="W6" t="s">
-        <v>45</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.036955</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.00718163265306122</v>
+      <c r="X6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>45</v>
       </c>
       <c r="Z6" t="n">
         <v>2.0</v>
@@ -2587,13 +2587,13 @@
         <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.02576140061176619</v>
+        <v>0.004042490889224566</v>
       </c>
       <c r="I7" t="n">
         <v>0.0886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07838883893931743</v>
+        <v>0.08127185838659269</v>
       </c>
       <c r="K7" t="s">
         <v>43</v>
@@ -2608,37 +2608,37 @@
         <v>49</v>
       </c>
       <c r="O7" t="n">
-        <v>0.036227973091514154</v>
+        <v>0.04225094883795314</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4770275902097947</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>324772.0</v>
-      </c>
-      <c r="R7" t="s">
+        <v>0.9237762275919041</v>
+      </c>
+      <c r="Q7" t="s">
         <v>49</v>
       </c>
+      <c r="R7" t="n">
+        <v>241898.0</v>
+      </c>
       <c r="S7" t="n">
+        <v>4251.0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>237647.0</v>
+      </c>
+      <c r="U7" t="n">
         <v>9.54E-8</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.0113857142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>45</v>
-      </c>
-      <c r="W7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.071191</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.0245357142857143</v>
+      <c r="X7" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>45</v>
       </c>
       <c r="Z7" t="n">
         <v>2.0</v>
@@ -2767,13 +2767,13 @@
         <v>0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>0.013211324428284068</v>
+        <v>-7.637973445428219E-4</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3861255363839027</v>
+        <v>0.542328528142503</v>
       </c>
       <c r="K2" t="s">
         <v>43</v>
@@ -2788,37 +2788,37 @@
         <v>50</v>
       </c>
       <c r="O2" t="n">
-        <v>0.012029158076366281</v>
+        <v>0.014023466414851929</v>
       </c>
       <c r="P2" t="n">
-        <v>0.27208439449816085</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>232809.0</v>
-      </c>
-      <c r="R2" t="s">
+        <v>0.9565641678357825</v>
+      </c>
+      <c r="Q2" t="s">
         <v>50</v>
       </c>
+      <c r="R2" t="n">
+        <v>174256.0</v>
+      </c>
       <c r="S2" t="n">
+        <v>28954.0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>145302.0</v>
+      </c>
+      <c r="U2" t="n">
         <v>2.1E-8</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>14009.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>0.0113683673469388</v>
       </c>
-      <c r="V2" t="s">
-        <v>45</v>
-      </c>
-      <c r="W2" t="s">
-        <v>45</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.063746</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.0113683673469388</v>
+      <c r="X2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>45</v>
       </c>
       <c r="Z2" t="n">
         <v>2.0</v>
@@ -2853,13 +2853,13 @@
         <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>-7.043450094299762E-4</v>
+        <v>0.004723583124410177</v>
       </c>
       <c r="I3" t="n">
         <v>0.3171</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2856375827394989</v>
+        <v>0.3473825865393444</v>
       </c>
       <c r="K3" t="s">
         <v>43</v>
@@ -2874,37 +2874,37 @@
         <v>50</v>
       </c>
       <c r="O3" t="n">
-        <v>0.010153915923388946</v>
+        <v>0.011879067804446688</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9446976272254781</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>232809.0</v>
-      </c>
-      <c r="R3" t="s">
+        <v>0.6908961541466597</v>
+      </c>
+      <c r="Q3" t="s">
         <v>50</v>
       </c>
+      <c r="R3" t="n">
+        <v>174256.0</v>
+      </c>
       <c r="S3" t="n">
+        <v>28954.0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>145302.0</v>
+      </c>
+      <c r="U3" t="n">
         <v>8.03E-9</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>49371.0</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.0069265306122449</v>
       </c>
-      <c r="V3" t="s">
-        <v>45</v>
-      </c>
-      <c r="W3" t="s">
-        <v>45</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-0.042572</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.0144209183673469</v>
+      <c r="X3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>45</v>
       </c>
       <c r="Z3" t="n">
         <v>2.0</v>
@@ -2939,13 +2939,13 @@
         <v>0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.004470800376588844</v>
+        <v>-0.01247889220385636</v>
       </c>
       <c r="I4" t="n">
         <v>0.6699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.41616088725092243</v>
+        <v>0.6019620558259113</v>
       </c>
       <c r="K4" t="s">
         <v>43</v>
@@ -2960,37 +2960,37 @@
         <v>50</v>
       </c>
       <c r="O4" t="n">
-        <v>0.013443474169917223</v>
+        <v>0.015701121684102908</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7394642735242606</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>232809.0</v>
-      </c>
-      <c r="R4" t="s">
+        <v>0.4267431650463671</v>
+      </c>
+      <c r="Q4" t="s">
         <v>50</v>
       </c>
+      <c r="R4" t="n">
+        <v>174256.0</v>
+      </c>
       <c r="S4" t="n">
+        <v>28954.0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>145302.0</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V4" t="s">
-        <v>45</v>
-      </c>
-      <c r="W4" t="s">
-        <v>45</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.041722</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.00684234693877551</v>
+      <c r="X4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>45</v>
       </c>
       <c r="Z4" t="n">
         <v>2.0</v>
@@ -3025,13 +3025,13 @@
         <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02100408358834647</v>
+        <v>0.022893289241710357</v>
       </c>
       <c r="I5" t="n">
         <v>0.0882</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07129878999523215</v>
+        <v>0.07372773390873198</v>
       </c>
       <c r="K5" t="s">
         <v>43</v>
@@ -3046,37 +3046,37 @@
         <v>50</v>
       </c>
       <c r="O5" t="n">
-        <v>0.014270943913311256</v>
+        <v>0.016719383083430885</v>
       </c>
       <c r="P5" t="n">
-        <v>0.14107284304206313</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>232809.0</v>
-      </c>
-      <c r="R5" t="s">
+        <v>0.17091602141197895</v>
+      </c>
+      <c r="Q5" t="s">
         <v>50</v>
       </c>
+      <c r="R5" t="n">
+        <v>174256.0</v>
+      </c>
       <c r="S5" t="n">
+        <v>28954.0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>145302.0</v>
+      </c>
+      <c r="U5" t="n">
         <v>7.76E-9</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>0.0114775510204082</v>
       </c>
-      <c r="V5" t="s">
-        <v>45</v>
-      </c>
-      <c r="W5" t="s">
-        <v>45</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-0.080535</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.0282632653061224</v>
+      <c r="X5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>45</v>
       </c>
       <c r="Z5" t="n">
         <v>2.0</v>
@@ -3111,13 +3111,13 @@
         <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0075008896559969965</v>
+        <v>-6.348876171356537E-4</v>
       </c>
       <c r="I6" t="n">
         <v>0.2786</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2553939065929582</v>
+        <v>0.30239991736296024</v>
       </c>
       <c r="K6" t="s">
         <v>43</v>
@@ -3132,37 +3132,37 @@
         <v>50</v>
       </c>
       <c r="O6" t="n">
-        <v>0.010051400112843665</v>
+        <v>0.011756938999462034</v>
       </c>
       <c r="P6" t="n">
-        <v>0.45551446708481336</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>232809.0</v>
-      </c>
-      <c r="R6" t="s">
+        <v>0.9569342893037607</v>
+      </c>
+      <c r="Q6" t="s">
         <v>50</v>
       </c>
+      <c r="R6" t="n">
+        <v>174256.0</v>
+      </c>
       <c r="S6" t="n">
+        <v>28954.0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>145302.0</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.72E-7</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.00718163265306122</v>
       </c>
-      <c r="V6" t="s">
-        <v>45</v>
-      </c>
-      <c r="W6" t="s">
-        <v>45</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.036955</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.00718163265306122</v>
+      <c r="X6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>45</v>
       </c>
       <c r="Z6" t="n">
         <v>2.0</v>
@@ -3197,13 +3197,13 @@
         <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>0.020498030949925836</v>
+        <v>0.028254122040445164</v>
       </c>
       <c r="I7" t="n">
         <v>0.0886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07822506861848125</v>
+        <v>0.0811650674869158</v>
       </c>
       <c r="K7" t="s">
         <v>43</v>
@@ -3218,37 +3218,37 @@
         <v>50</v>
       </c>
       <c r="O7" t="n">
-        <v>0.013739531362455648</v>
+        <v>0.016061244771371917</v>
       </c>
       <c r="P7" t="n">
-        <v>0.13572490258994566</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>232809.0</v>
-      </c>
-      <c r="R7" t="s">
+        <v>0.07855221077770613</v>
+      </c>
+      <c r="Q7" t="s">
         <v>50</v>
       </c>
+      <c r="R7" t="n">
+        <v>174256.0</v>
+      </c>
       <c r="S7" t="n">
+        <v>28954.0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>145302.0</v>
+      </c>
+      <c r="U7" t="n">
         <v>9.54E-8</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.0113857142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>45</v>
-      </c>
-      <c r="W7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.071191</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.0245357142857143</v>
+      <c r="X7" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>45</v>
       </c>
       <c r="Z7" t="n">
         <v>2.0</v>
@@ -3377,13 +3377,13 @@
         <v>0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.02541077373875312</v>
+        <v>-0.028507750897813898</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3863387461620198</v>
+        <v>0.542516627530205</v>
       </c>
       <c r="K2" t="s">
         <v>43</v>
@@ -3398,37 +3398,37 @@
         <v>51</v>
       </c>
       <c r="O2" t="n">
-        <v>0.021726510957283177</v>
+        <v>0.025559976958568913</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2421722340151009</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>306802.0</v>
-      </c>
-      <c r="R2" t="s">
+        <v>0.26471000961174834</v>
+      </c>
+      <c r="Q2" t="s">
         <v>51</v>
       </c>
+      <c r="R2" t="n">
+        <v>228687.0</v>
+      </c>
       <c r="S2" t="n">
+        <v>8598.0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>220089.0</v>
+      </c>
+      <c r="U2" t="n">
         <v>2.1E-8</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>14009.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>0.0113683673469388</v>
       </c>
-      <c r="V2" t="s">
-        <v>45</v>
-      </c>
-      <c r="W2" t="s">
-        <v>45</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.063746</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.0113683673469388</v>
+      <c r="X2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>45</v>
       </c>
       <c r="Z2" t="n">
         <v>2.0</v>
@@ -3463,13 +3463,13 @@
         <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01321523652819153</v>
+        <v>0.034059088686929646</v>
       </c>
       <c r="I3" t="n">
         <v>0.3171</v>
       </c>
       <c r="J3" t="n">
-        <v>0.28551639167932413</v>
+        <v>0.3471098051047939</v>
       </c>
       <c r="K3" t="s">
         <v>43</v>
@@ -3484,37 +3484,37 @@
         <v>51</v>
       </c>
       <c r="O3" t="n">
-        <v>0.018533218618133722</v>
+        <v>0.021846406975565506</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4758106446035647</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>306802.0</v>
-      </c>
-      <c r="R3" t="s">
+        <v>0.11899052763121414</v>
+      </c>
+      <c r="Q3" t="s">
         <v>51</v>
       </c>
+      <c r="R3" t="n">
+        <v>228687.0</v>
+      </c>
       <c r="S3" t="n">
+        <v>8598.0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>220089.0</v>
+      </c>
+      <c r="U3" t="n">
         <v>8.03E-9</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>49371.0</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.0069265306122449</v>
       </c>
-      <c r="V3" t="s">
-        <v>45</v>
-      </c>
-      <c r="W3" t="s">
-        <v>45</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-0.042572</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.0144209183673469</v>
+      <c r="X3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>45</v>
       </c>
       <c r="Z3" t="n">
         <v>2.0</v>
@@ -3549,13 +3549,13 @@
         <v>0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.03237005824445815</v>
+        <v>-0.03585864896824078</v>
       </c>
       <c r="I4" t="n">
         <v>0.6699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.41629943742218106</v>
+        <v>0.6019778124685706</v>
       </c>
       <c r="K4" t="s">
         <v>43</v>
@@ -3570,37 +3570,37 @@
         <v>51</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02429420763830611</v>
+        <v>0.02859319991141303</v>
       </c>
       <c r="P4" t="n">
-        <v>0.18272261779928556</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>306802.0</v>
-      </c>
-      <c r="R4" t="s">
+        <v>0.20980671585189614</v>
+      </c>
+      <c r="Q4" t="s">
         <v>51</v>
       </c>
+      <c r="R4" t="n">
+        <v>228687.0</v>
+      </c>
       <c r="S4" t="n">
+        <v>8598.0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>220089.0</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V4" t="s">
-        <v>45</v>
-      </c>
-      <c r="W4" t="s">
-        <v>45</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.041722</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.00684234693877551</v>
+      <c r="X4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>45</v>
       </c>
       <c r="Z4" t="n">
         <v>2.0</v>
@@ -3635,13 +3635,13 @@
         <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>0.018808687601383066</v>
+        <v>0.034923813495659886</v>
       </c>
       <c r="I5" t="n">
         <v>0.0882</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07141250708926278</v>
+        <v>0.07382798322598136</v>
       </c>
       <c r="K5" t="s">
         <v>43</v>
@@ -3656,37 +3656,37 @@
         <v>51</v>
       </c>
       <c r="O5" t="n">
-        <v>0.026019190793507396</v>
+        <v>0.0305176670933387</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4697551478144027</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>306802.0</v>
-      </c>
-      <c r="R5" t="s">
+        <v>0.25246600242121087</v>
+      </c>
+      <c r="Q5" t="s">
         <v>51</v>
       </c>
+      <c r="R5" t="n">
+        <v>228687.0</v>
+      </c>
       <c r="S5" t="n">
+        <v>8598.0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>220089.0</v>
+      </c>
+      <c r="U5" t="n">
         <v>7.76E-9</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>0.0114775510204082</v>
       </c>
-      <c r="V5" t="s">
-        <v>45</v>
-      </c>
-      <c r="W5" t="s">
-        <v>45</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-0.080535</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.0282632653061224</v>
+      <c r="X5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>45</v>
       </c>
       <c r="Z5" t="n">
         <v>2.0</v>
@@ -3721,13 +3721,13 @@
         <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>0.026755660901255824</v>
+        <v>0.028118363490912946</v>
       </c>
       <c r="I6" t="n">
         <v>0.2786</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2553177619441855</v>
+        <v>0.3023127681066261</v>
       </c>
       <c r="K6" t="s">
         <v>43</v>
@@ -3742,37 +3742,37 @@
         <v>51</v>
       </c>
       <c r="O6" t="n">
-        <v>0.018336926204178518</v>
+        <v>0.0215831133340729</v>
       </c>
       <c r="P6" t="n">
-        <v>0.14453380620675035</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>306802.0</v>
-      </c>
-      <c r="R6" t="s">
+        <v>0.19264489502154045</v>
+      </c>
+      <c r="Q6" t="s">
         <v>51</v>
       </c>
+      <c r="R6" t="n">
+        <v>228687.0</v>
+      </c>
       <c r="S6" t="n">
+        <v>8598.0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>220089.0</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.72E-7</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.00718163265306122</v>
       </c>
-      <c r="V6" t="s">
-        <v>45</v>
-      </c>
-      <c r="W6" t="s">
-        <v>45</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.036955</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.00718163265306122</v>
+      <c r="X6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>45</v>
       </c>
       <c r="Z6" t="n">
         <v>2.0</v>
@@ -3807,13 +3807,13 @@
         <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>2.6091172210830654E-4</v>
+        <v>0.0174348357204698</v>
       </c>
       <c r="I7" t="n">
         <v>0.0886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07829968513894955</v>
+        <v>0.08118520073287944</v>
       </c>
       <c r="K7" t="s">
         <v>43</v>
@@ -3828,37 +3828,37 @@
         <v>51</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02521583489929918</v>
+        <v>0.02957462817332391</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9917443256984703</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>306802.0</v>
-      </c>
-      <c r="R7" t="s">
+        <v>0.5555124788826422</v>
+      </c>
+      <c r="Q7" t="s">
         <v>51</v>
       </c>
+      <c r="R7" t="n">
+        <v>228687.0</v>
+      </c>
       <c r="S7" t="n">
+        <v>8598.0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>220089.0</v>
+      </c>
+      <c r="U7" t="n">
         <v>9.54E-8</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.0113857142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>45</v>
-      </c>
-      <c r="W7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.071191</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.0245357142857143</v>
+      <c r="X7" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>45</v>
       </c>
       <c r="Z7" t="n">
         <v>2.0</v>
